--- a/data/trans_dic/PCS12_SP_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/PCS12_SP_R2-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12)</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,83; 50,87</t>
+          <t>38,84; 50,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,9; 57,22</t>
+          <t>45,08; 56,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,05; 51,2</t>
+          <t>39,95; 51,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52,55; 67,28</t>
+          <t>53,18; 67,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,42; 63,35</t>
+          <t>50,78; 63,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,23; 61,64</t>
+          <t>49,12; 61,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,46; 60,86</t>
+          <t>48,55; 60,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>74,62; 83,3</t>
+          <t>75,33; 83,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46,71; 55,84</t>
+          <t>46,21; 55,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48,97; 57,28</t>
+          <t>48,86; 57,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45,75; 54,24</t>
+          <t>45,29; 54,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,14; 74,19</t>
+          <t>64,75; 74,01</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>44,39; 53,59</t>
+          <t>43,55; 53,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,86; 55,39</t>
+          <t>46,32; 55,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,84; 49,63</t>
+          <t>40,61; 49,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39,21; 50,93</t>
+          <t>39,19; 50,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>54,17; 63,23</t>
+          <t>54,76; 63,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,72; 67,84</t>
+          <t>59,52; 67,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,45; 57,8</t>
+          <t>49,09; 57,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>51,89; 60,09</t>
+          <t>52,2; 59,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,46; 56,87</t>
+          <t>50,65; 57,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53,98; 60,55</t>
+          <t>53,89; 60,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45,83; 52,16</t>
+          <t>46,03; 52,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,2; 54,06</t>
+          <t>46,59; 53,5</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,16; 48,11</t>
+          <t>36,81; 47,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36,98; 47,99</t>
+          <t>36,39; 48,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,44; 35,54</t>
+          <t>25,42; 34,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46,59; 58,32</t>
+          <t>46,66; 58,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,17; 74,09</t>
+          <t>64,09; 74,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,01; 58,22</t>
+          <t>47,32; 58,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,07; 38,72</t>
+          <t>28,94; 39,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47,55; 56,32</t>
+          <t>47,12; 56,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52,23; 59,99</t>
+          <t>52,2; 60,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43,7; 51,49</t>
+          <t>43,79; 51,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28,79; 35,68</t>
+          <t>28,17; 35,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,48; 55,89</t>
+          <t>48,44; 55,88</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,1; 46,17</t>
+          <t>36,02; 45,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,05; 42,76</t>
+          <t>32,25; 42,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,31; 60,85</t>
+          <t>50,59; 61,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41,7; 57,33</t>
+          <t>42,07; 56,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,51; 65,45</t>
+          <t>55,58; 64,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,48; 55,74</t>
+          <t>45,93; 55,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,48; 68,73</t>
+          <t>58,2; 68,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,27; 52,46</t>
+          <t>25,0; 53,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47,65; 55,14</t>
+          <t>47,08; 54,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40,56; 48,03</t>
+          <t>40,47; 47,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56,37; 63,56</t>
+          <t>56,03; 63,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,55; 51,94</t>
+          <t>31,12; 51,52</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,03; 41,0</t>
+          <t>27,6; 40,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37,53; 51,67</t>
+          <t>37,14; 51,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,3; 37,34</t>
+          <t>25,03; 37,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35,74; 48,27</t>
+          <t>35,97; 47,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>41,55; 55,48</t>
+          <t>42,65; 57,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,86; 64,69</t>
+          <t>51,24; 65,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,95; 45,83</t>
+          <t>32,76; 46,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>48,11; 57,81</t>
+          <t>47,8; 57,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36,69; 46,36</t>
+          <t>36,74; 46,19</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46,85; 56,37</t>
+          <t>46,47; 56,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,71; 39,58</t>
+          <t>30,74; 39,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>43,81; 52,0</t>
+          <t>43,88; 51,43</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,08; 48,76</t>
+          <t>37,29; 49,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41,53; 54,01</t>
+          <t>41,17; 53,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,43; 40,49</t>
+          <t>29,16; 40,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49,34; 60,52</t>
+          <t>49,48; 60,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63,06; 74,09</t>
+          <t>62,88; 73,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49,49; 61,45</t>
+          <t>49,9; 62,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,0; 51,16</t>
+          <t>39,64; 51,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>57,2; 66,94</t>
+          <t>57,2; 67,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52,0; 60,06</t>
+          <t>51,73; 60,53</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46,95; 55,95</t>
+          <t>47,26; 55,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36,11; 44,82</t>
+          <t>36,14; 45,03</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>54,56; 62,3</t>
+          <t>54,51; 61,97</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41,62; 50,3</t>
+          <t>41,86; 49,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37,63; 45,52</t>
+          <t>37,56; 45,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34,12; 42,38</t>
+          <t>34,61; 42,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42,82; 52,67</t>
+          <t>43,16; 52,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>53,43; 61,3</t>
+          <t>53,32; 61,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,57; 56,92</t>
+          <t>49,44; 56,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,56; 53,0</t>
+          <t>45,51; 52,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>50,38; 84,6</t>
+          <t>50,67; 82,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>48,5; 54,49</t>
+          <t>48,71; 54,66</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44,65; 50,28</t>
+          <t>44,77; 50,22</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41,34; 47,0</t>
+          <t>41,48; 47,13</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>49,21; 75,47</t>
+          <t>48,83; 75,07</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>34,7; 42,19</t>
+          <t>34,58; 42,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>38,04; 45,33</t>
+          <t>37,76; 45,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28,53; 35,36</t>
+          <t>28,91; 35,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30,29; 77,16</t>
+          <t>30,41; 76,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>43,64; 50,65</t>
+          <t>43,32; 50,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,13; 53,43</t>
+          <t>45,89; 53,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,65; 45,76</t>
+          <t>39,04; 46,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>37,97; 44,2</t>
+          <t>37,59; 43,92</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>40,18; 45,17</t>
+          <t>40,22; 45,3</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43,14; 48,48</t>
+          <t>43,11; 48,68</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34,63; 39,75</t>
+          <t>34,78; 39,82</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>35,56; 66,64</t>
+          <t>35,56; 68,43</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40,98; 44,5</t>
+          <t>40,73; 44,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42,18; 45,89</t>
+          <t>42,44; 45,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37,42; 40,7</t>
+          <t>37,29; 40,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45,22; 61,45</t>
+          <t>45,41; 60,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>55,36; 58,85</t>
+          <t>55,21; 58,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52,61; 56,21</t>
+          <t>52,67; 56,06</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45,97; 49,62</t>
+          <t>46,23; 49,6</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>50,93; 63,17</t>
+          <t>50,94; 63,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>48,6; 51,16</t>
+          <t>48,72; 51,17</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48,01; 50,45</t>
+          <t>47,99; 50,47</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42,23; 44,64</t>
+          <t>42,19; 44,71</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>49,01; 58,43</t>
+          <t>49,02; 58,99</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12)</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>106015; 138869</t>
+          <t>106042; 138826</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>132343; 168657</t>
+          <t>132875; 166591</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>114726; 150398</t>
+          <t>117372; 152678</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>163677; 209539</t>
+          <t>165620; 209758</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>131518; 165242</t>
+          <t>132451; 164675</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>141418; 177060</t>
+          <t>141082; 176719</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>139900; 175713</t>
+          <t>140153; 174011</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>216113; 241252</t>
+          <t>218191; 242760</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>249366; 298082</t>
+          <t>246697; 294011</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>284996; 333385</t>
+          <t>284353; 336112</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>266461; 315937</t>
+          <t>263786; 316316</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>391564; 445948</t>
+          <t>389221; 444879</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>218900; 264248</t>
+          <t>214727; 262900</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>231836; 280027</t>
+          <t>234172; 280899</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>205275; 249418</t>
+          <t>204083; 251240</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>202924; 263575</t>
+          <t>202796; 259856</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>273009; 318640</t>
+          <t>275968; 319840</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>312805; 355335</t>
+          <t>311736; 354418</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>253415; 302349</t>
+          <t>256773; 300761</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>266471; 308593</t>
+          <t>268097; 305853</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>503075; 566982</t>
+          <t>504944; 569597</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>555594; 623189</t>
+          <t>554677; 620159</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>470043; 535026</t>
+          <t>472117; 538575</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>486688; 557417</t>
+          <t>480363; 551589</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>118475; 153410</t>
+          <t>117361; 152885</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>119847; 155499</t>
+          <t>117920; 155539</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81050; 113216</t>
+          <t>80965; 111402</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>146315; 183177</t>
+          <t>146549; 182277</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>215242; 248492</t>
+          <t>214974; 248616</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>160320; 198549</t>
+          <t>161382; 198160</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94395; 130230</t>
+          <t>97332; 131807</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>163620; 193800</t>
+          <t>162150; 195687</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>341748; 392507</t>
+          <t>341496; 392611</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>290642; 342419</t>
+          <t>291242; 344177</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>188532; 233629</t>
+          <t>184480; 231817</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>319092; 367864</t>
+          <t>318851; 367790</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>129475; 165603</t>
+          <t>129183; 164523</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>119876; 159897</t>
+          <t>120591; 159332</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>186141; 225114</t>
+          <t>187181; 227146</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>127666; 175525</t>
+          <t>128819; 171910</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>206205; 243127</t>
+          <t>206454; 240969</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>176887; 216820</t>
+          <t>178654; 217556</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>226466; 266172</t>
+          <t>225413; 266683</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>123595; 246813</t>
+          <t>117621; 251654</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>347881; 402560</t>
+          <t>343754; 397841</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>309450; 366413</t>
+          <t>308753; 365954</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>426872; 481310</t>
+          <t>424298; 479978</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>252782; 403416</t>
+          <t>241723; 400160</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>56997; 83366</t>
+          <t>56116; 83228</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>79790; 109856</t>
+          <t>78960; 110530</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51334; 78878</t>
+          <t>52875; 79877</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63711; 86038</t>
+          <t>64104; 85435</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>86294; 115218</t>
+          <t>88564; 118427</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>111693; 142043</t>
+          <t>112510; 142761</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>72028; 100184</t>
+          <t>71608; 101500</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>99413; 119471</t>
+          <t>98774; 119330</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>150787; 190519</t>
+          <t>150984; 189827</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>202487; 243624</t>
+          <t>200845; 243878</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>132011; 170119</t>
+          <t>132118; 170545</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>168606; 200158</t>
+          <t>168884; 197946</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>100415; 132041</t>
+          <t>100985; 133584</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>113783; 147978</t>
+          <t>112800; 146889</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77444; 106535</t>
+          <t>76717; 107672</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>132798; 162887</t>
+          <t>133176; 163608</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>175392; 206086</t>
+          <t>174890; 205251</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>138583; 172074</t>
+          <t>139741; 173813</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>106526; 139730</t>
+          <t>108264; 140916</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>147029; 172086</t>
+          <t>147027; 172960</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>285478; 329697</t>
+          <t>283971; 332294</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>260095; 309974</t>
+          <t>261840; 309788</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>193659; 240353</t>
+          <t>193816; 241443</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>287093; 327854</t>
+          <t>286837; 326090</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>255972; 309330</t>
+          <t>257425; 306780</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>249402; 301679</t>
+          <t>248911; 303875</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>224020; 278221</t>
+          <t>227260; 276781</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>265471; 326491</t>
+          <t>267566; 327210</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>341002; 391247</t>
+          <t>340319; 390800</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>337012; 394912</t>
+          <t>343014; 395444</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>314958; 366399</t>
+          <t>314631; 365758</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>426634; 716421</t>
+          <t>429115; 698925</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>607787; 682840</t>
+          <t>610493; 685035</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>605749; 682125</t>
+          <t>607412; 681297</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>557196; 633428</t>
+          <t>559045; 635211</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>721843; 1106900</t>
+          <t>716268; 1101041</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>258063; 313824</t>
+          <t>257197; 314474</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>296407; 353156</t>
+          <t>294183; 352342</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>222168; 275323</t>
+          <t>225099; 275246</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>280887; 715435</t>
+          <t>281912; 712108</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>341954; 396812</t>
+          <t>339401; 395676</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>380061; 440156</t>
+          <t>378048; 437205</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>319333; 378052</t>
+          <t>322558; 380309</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>271563; 316113</t>
+          <t>268889; 314109</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>613690; 689956</t>
+          <t>614246; 691914</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>691466; 777035</t>
+          <t>691057; 780360</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>555786; 637914</t>
+          <t>558082; 639015</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>584051; 1094590</t>
+          <t>584079; 1123850</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1342788; 1458215</t>
+          <t>1334686; 1458948</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1445255; 1572564</t>
+          <t>1454404; 1573064</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1270293; 1381491</t>
+          <t>1265887; 1383208</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1557120; 2116180</t>
+          <t>1563703; 2095632</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1870650; 1988583</t>
+          <t>1865497; 1982855</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1871924; 2000271</t>
+          <t>1874277; 1994639</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1629512; 1758713</t>
+          <t>1638475; 1758059</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1855580; 2301535</t>
+          <t>1855890; 2301980</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3234788; 3405160</t>
+          <t>3242413; 3406066</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3353430; 3524304</t>
+          <t>3351809; 3525395</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2930007; 3097352</t>
+          <t>2927561; 3102177</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3473685; 4140835</t>
+          <t>3474211; 4180808</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/PCS12_SP_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/PCS12_SP_R2-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>70,96%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,84; 50,85</t>
+          <t>39,19; 51,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45,08; 56,52</t>
+          <t>44,76; 56,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,95; 51,97</t>
+          <t>39,34; 51,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53,18; 67,35</t>
+          <t>57,27; 68,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,78; 63,13</t>
+          <t>50,01; 62,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,12; 61,52</t>
+          <t>49,62; 61,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,55; 60,27</t>
+          <t>48,23; 60,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>75,33; 83,82</t>
+          <t>74,39; 82,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46,21; 55,07</t>
+          <t>46,27; 54,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48,86; 57,75</t>
+          <t>48,99; 57,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45,29; 54,31</t>
+          <t>45,72; 54,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64,75; 74,01</t>
+          <t>67,31; 74,39</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,26%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>43,55; 53,32</t>
+          <t>43,97; 52,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,32; 55,57</t>
+          <t>46,0; 55,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,61; 49,99</t>
+          <t>40,81; 49,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39,19; 50,21</t>
+          <t>39,71; 50,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>54,76; 63,47</t>
+          <t>54,52; 62,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,52; 67,67</t>
+          <t>59,46; 68,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,09; 57,5</t>
+          <t>49,19; 57,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,2; 59,55</t>
+          <t>51,46; 59,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,65; 57,13</t>
+          <t>50,74; 57,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53,89; 60,25</t>
+          <t>53,98; 60,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46,03; 52,51</t>
+          <t>46,15; 52,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>46,59; 53,5</t>
+          <t>46,61; 53,67</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,81; 47,95</t>
+          <t>36,28; 47,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36,39; 48,0</t>
+          <t>37,24; 47,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,42; 34,97</t>
+          <t>25,67; 35,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46,66; 58,04</t>
+          <t>47,68; 58,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,09; 74,12</t>
+          <t>63,71; 73,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,32; 58,11</t>
+          <t>47,12; 58,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,94; 39,19</t>
+          <t>28,55; 39,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47,12; 56,87</t>
+          <t>47,12; 56,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52,2; 60,01</t>
+          <t>52,1; 59,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43,79; 51,75</t>
+          <t>43,53; 51,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28,17; 35,4</t>
+          <t>28,39; 35,92</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,44; 55,88</t>
+          <t>48,82; 55,61</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>49,95%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,02; 45,87</t>
+          <t>35,99; 46,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,25; 42,6</t>
+          <t>32,59; 42,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,59; 61,4</t>
+          <t>50,82; 61,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42,07; 56,15</t>
+          <t>38,88; 52,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,58; 64,87</t>
+          <t>55,44; 65,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,93; 55,93</t>
+          <t>44,67; 55,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,2; 68,86</t>
+          <t>58,95; 68,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,0; 53,49</t>
+          <t>48,4; 58,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47,08; 54,49</t>
+          <t>47,29; 54,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40,47; 47,97</t>
+          <t>40,64; 48,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56,03; 63,38</t>
+          <t>56,11; 63,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,12; 51,52</t>
+          <t>45,44; 54,1</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>45,96%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,6; 40,94</t>
+          <t>27,55; 41,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37,14; 51,99</t>
+          <t>37,43; 51,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,03; 37,82</t>
+          <t>25,07; 37,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35,97; 47,93</t>
+          <t>34,25; 45,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>42,65; 57,03</t>
+          <t>41,57; 56,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,24; 65,01</t>
+          <t>51,11; 64,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,76; 46,43</t>
+          <t>32,57; 45,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>47,8; 57,75</t>
+          <t>46,46; 56,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36,74; 46,19</t>
+          <t>36,46; 46,79</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46,47; 56,43</t>
+          <t>46,12; 56,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,74; 39,68</t>
+          <t>30,71; 40,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>43,88; 51,43</t>
+          <t>41,94; 49,93</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,41%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,29; 49,33</t>
+          <t>37,37; 49,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41,17; 53,61</t>
+          <t>41,46; 54,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,16; 40,92</t>
+          <t>29,11; 40,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49,48; 60,78</t>
+          <t>49,6; 60,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>62,88; 73,79</t>
+          <t>63,52; 74,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49,9; 62,07</t>
+          <t>49,25; 61,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,64; 51,6</t>
+          <t>39,69; 51,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>57,2; 67,28</t>
+          <t>57,05; 67,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>51,73; 60,53</t>
+          <t>52,08; 60,56</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>47,26; 55,92</t>
+          <t>47,1; 56,09</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36,14; 45,03</t>
+          <t>36,13; 44,49</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>54,51; 61,97</t>
+          <t>54,61; 62,28</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>50,63%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41,86; 49,88</t>
+          <t>41,53; 49,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37,56; 45,85</t>
+          <t>37,5; 45,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34,61; 42,16</t>
+          <t>34,15; 42,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43,16; 52,78</t>
+          <t>44,81; 53,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>53,32; 61,23</t>
+          <t>52,95; 61,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,44; 56,99</t>
+          <t>49,25; 56,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,51; 52,91</t>
+          <t>45,46; 52,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>50,67; 82,53</t>
+          <t>48,38; 55,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>48,71; 54,66</t>
+          <t>48,74; 54,15</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44,77; 50,22</t>
+          <t>44,84; 49,99</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41,48; 47,13</t>
+          <t>41,22; 46,6</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>48,83; 75,07</t>
+          <t>47,93; 53,35</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>35,41%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>34,58; 42,28</t>
+          <t>34,58; 42,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>37,76; 45,22</t>
+          <t>38,0; 45,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28,91; 35,35</t>
+          <t>28,41; 35,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30,41; 76,8</t>
+          <t>27,69; 34,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>43,32; 50,5</t>
+          <t>43,42; 50,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,89; 53,07</t>
+          <t>46,29; 53,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,04; 46,03</t>
+          <t>38,55; 45,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>37,59; 43,92</t>
+          <t>36,76; 43,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>40,22; 45,3</t>
+          <t>40,22; 45,49</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43,11; 48,68</t>
+          <t>43,12; 48,07</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34,78; 39,82</t>
+          <t>35,06; 39,82</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>35,56; 68,43</t>
+          <t>33,24; 37,79</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>49,31%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40,73; 44,53</t>
+          <t>40,72; 44,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42,44; 45,91</t>
+          <t>42,17; 45,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37,29; 40,75</t>
+          <t>37,42; 40,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45,41; 60,85</t>
+          <t>43,74; 47,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>55,21; 58,68</t>
+          <t>55,26; 58,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52,67; 56,06</t>
+          <t>52,73; 55,95</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,23; 49,6</t>
+          <t>46,06; 49,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>50,94; 63,18</t>
+          <t>51,61; 54,53</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>48,72; 51,17</t>
+          <t>48,72; 51,26</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>47,99; 50,47</t>
+          <t>48,15; 50,48</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42,19; 44,71</t>
+          <t>42,2; 44,66</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>49,02; 58,99</t>
+          <t>48,13; 50,47</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>189437</t>
+          <t>201403</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>231287</t>
+          <t>249100</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>420723</t>
+          <t>450503</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>106042; 138826</t>
+          <t>106991; 139227</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>132875; 166591</t>
+          <t>131932; 167800</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>117372; 152678</t>
+          <t>115554; 151734</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>165620; 209758</t>
+          <t>182589; 219357</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>132451; 164675</t>
+          <t>130452; 163527</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>141082; 176719</t>
+          <t>142525; 177764</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>140153; 174011</t>
+          <t>139253; 174077</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>218191; 242760</t>
+          <t>235124; 260487</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>246697; 294011</t>
+          <t>247016; 292980</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>284353; 336112</t>
+          <t>285119; 334302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>263786; 316316</t>
+          <t>266300; 314612</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>389221; 444879</t>
+          <t>427369; 472289</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>232177</t>
+          <t>238211</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>287324</t>
+          <t>301924</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>519501</t>
+          <t>540134</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>214727; 262900</t>
+          <t>216828; 260604</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>234172; 280899</t>
+          <t>232523; 279058</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>204083; 251240</t>
+          <t>205105; 250265</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>202796; 259856</t>
+          <t>210339; 266545</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>275968; 319840</t>
+          <t>274764; 317410</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>311736; 354418</t>
+          <t>311409; 357325</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>256773; 300761</t>
+          <t>257301; 301015</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>268097; 305853</t>
+          <t>280500; 324006</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>504944; 569597</t>
+          <t>505908; 568608</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>554677; 620159</t>
+          <t>555659; 620523</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>472117; 538575</t>
+          <t>473384; 541293</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>480363; 551589</t>
+          <t>500907; 576821</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>164971</t>
+          <t>165679</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>178911</t>
+          <t>182010</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>343882</t>
+          <t>347690</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>117361; 152885</t>
+          <t>115684; 152212</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>117920; 155539</t>
+          <t>120680; 154871</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80965; 111402</t>
+          <t>81777; 112595</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>146549; 182277</t>
+          <t>149743; 184708</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>214974; 248616</t>
+          <t>213681; 247483</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>161382; 198160</t>
+          <t>160706; 198287</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97332; 131807</t>
+          <t>96019; 131205</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>162150; 195687</t>
+          <t>165588; 197152</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>341496; 392611</t>
+          <t>340894; 392093</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>291242; 344177</t>
+          <t>289522; 340855</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>184480; 231817</t>
+          <t>185901; 235231</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>318851; 367790</t>
+          <t>324879; 370096</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>150201</t>
+          <t>167904</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>198363</t>
+          <t>222985</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>348564</t>
+          <t>390889</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>129183; 164523</t>
+          <t>129084; 166027</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>120591; 159332</t>
+          <t>121884; 159807</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>187181; 227146</t>
+          <t>188022; 225931</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>128819; 171910</t>
+          <t>142360; 193302</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>206454; 240969</t>
+          <t>205925; 243199</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>178654; 217556</t>
+          <t>173742; 215080</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>225413; 266683</t>
+          <t>228289; 266432</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>117621; 251654</t>
+          <t>201547; 243034</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>343754; 397841</t>
+          <t>345306; 399259</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>308753; 365954</t>
+          <t>310028; 367611</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>424298; 479978</t>
+          <t>424864; 481169</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>241723; 400160</t>
+          <t>355607; 423329</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74067</t>
+          <t>82459</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>109185</t>
+          <t>115290</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>183251</t>
+          <t>197750</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>56116; 83228</t>
+          <t>56020; 83424</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>78960; 110530</t>
+          <t>79579; 109577</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52875; 79877</t>
+          <t>52943; 79983</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>64104; 85435</t>
+          <t>70271; 94313</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>88564; 118427</t>
+          <t>86325; 116663</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>112510; 142761</t>
+          <t>112226; 142382</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>71608; 101500</t>
+          <t>71200; 99866</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>98774; 119330</t>
+          <t>104595; 126175</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>150984; 189827</t>
+          <t>149829; 192286</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>200845; 243878</t>
+          <t>199343; 242237</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>132118; 170545</t>
+          <t>131973; 172151</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>168884; 197946</t>
+          <t>180491; 214874</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>147654</t>
+          <t>147551</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>159462</t>
+          <t>164348</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>307116</t>
+          <t>311899</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>100985; 133584</t>
+          <t>101207; 133401</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>112800; 146889</t>
+          <t>113605; 147973</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>76717; 107672</t>
+          <t>76595; 107286</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>133176; 163608</t>
+          <t>134025; 162865</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>174890; 205251</t>
+          <t>176672; 206055</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>139741; 173813</t>
+          <t>137923; 172074</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>108264; 140916</t>
+          <t>108400; 140980</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>147027; 172960</t>
+          <t>150481; 177517</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>283971; 332294</t>
+          <t>285886; 332466</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>261840; 309788</t>
+          <t>260963; 310745</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>193816; 241443</t>
+          <t>193754; 238582</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>286837; 326090</t>
+          <t>291581; 332545</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>297941</t>
+          <t>351330</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>536702</t>
+          <t>399966</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>834644</t>
+          <t>751297</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>257425; 306780</t>
+          <t>255391; 306181</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>248911; 303875</t>
+          <t>248533; 303419</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>227260; 276781</t>
+          <t>224230; 275959</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>267566; 327210</t>
+          <t>320216; 382601</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>340319; 390800</t>
+          <t>337929; 392597</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>343014; 395444</t>
+          <t>341693; 394306</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>314631; 365758</t>
+          <t>314269; 366146</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>429115; 698925</t>
+          <t>372221; 423944</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>610493; 685035</t>
+          <t>610844; 678692</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>607412; 681297</t>
+          <t>608354; 678125</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>559045; 635211</t>
+          <t>555550; 628076</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>716268; 1101041</t>
+          <t>711239; 791738</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>458464</t>
+          <t>244018</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>292559</t>
+          <t>331352</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>751023</t>
+          <t>575370</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>257197; 314474</t>
+          <t>257183; 313105</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>294183; 352342</t>
+          <t>296042; 355595</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>225099; 275246</t>
+          <t>221225; 275046</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>281912; 712108</t>
+          <t>220537; 271922</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>339401; 395676</t>
+          <t>340189; 398472</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>378048; 437205</t>
+          <t>381322; 443034</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>322558; 380309</t>
+          <t>318517; 378821</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>268889; 314109</t>
+          <t>304572; 356640</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>614246; 691914</t>
+          <t>614349; 694816</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>691057; 780360</t>
+          <t>691260; 770543</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>558082; 639015</t>
+          <t>562662; 639052</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>584079; 1123850</t>
+          <t>540049; 614090</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1714911</t>
+          <t>1598557</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1993792</t>
+          <t>1966976</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3708703</t>
+          <t>3565533</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1334686; 1458948</t>
+          <t>1334087; 1455877</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1454404; 1573064</t>
+          <t>1445018; 1567650</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1265887; 1383208</t>
+          <t>1270190; 1384774</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1563703; 2095632</t>
+          <t>1537537; 1660921</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1865497; 1982855</t>
+          <t>1867507; 1984856</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1874277; 1994639</t>
+          <t>1876130; 1990743</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1638475; 1758059</t>
+          <t>1632684; 1752258</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1855890; 2301980</t>
+          <t>1917711; 2026014</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3242413; 3406066</t>
+          <t>3242541; 3411872</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3351809; 3525395</t>
+          <t>3363111; 3526124</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2927561; 3102177</t>
+          <t>2928023; 3099135</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3474211; 4180808</t>
+          <t>3480317; 3649031</t>
         </is>
       </c>
     </row>
